--- a/information_request_forms/006_low_code_development_consultation_request--information_request_forms.xlsx
+++ b/information_request_forms/006_low_code_development_consultation_request--information_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1079,8 +1079,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'new_project'}</t>
+          <t>new_project</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'New Project'}</t>
+          <t>New Project</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'existing_project'}</t>
+          <t>existing_project</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Existing Project'}</t>
+          <t>Existing Project</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'phone_call'}</t>
+          <t>phone_call</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Phone Call'}</t>
+          <t>Phone Call</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'meeting'}</t>
+          <t>meeting</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Meeting'}</t>
+          <t>Meeting</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'new_application'}</t>
+          <t>new_application</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'New Application'}</t>
+          <t>New Application</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'existing_application'}</t>
+          <t>existing_application</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Existing Application'}</t>
+          <t>Existing Application</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'new_service'}</t>
+          <t>new_service</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'New Service'}</t>
+          <t>New Service</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'existing_service'}</t>
+          <t>existing_service</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Existing Service'}</t>
+          <t>Existing Service</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'project_completion'}</t>
+          <t>project_completion</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Project Completion'}</t>
+          <t>Project Completion</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'project_continuation'}</t>
+          <t>project_continuation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Project Continuation'}</t>
+          <t>Project Continuation</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'project_closure'}</t>
+          <t>project_closure</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Project Closure'}</t>
+          <t>Project Closure</t>
         </is>
       </c>
     </row>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'project_delay'}</t>
+          <t>project_delay</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Project Delay'}</t>
+          <t>Project Delay</t>
         </is>
       </c>
     </row>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1363,12 +1363,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'New'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'existing'}</t>
+          <t>existing</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Existing'}</t>
+          <t>Existing</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'front-end'}</t>
+          <t>front-end</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Front-end'}</t>
+          <t>Front-end</t>
         </is>
       </c>
     </row>
@@ -1448,12 +1448,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'back-end'}</t>
+          <t>back-end</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Back-end'}</t>
+          <t>Back-end</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'full-stack'}</t>
+          <t>full-stack</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Full-stack'}</t>
+          <t>Full-stack</t>
         </is>
       </c>
     </row>
@@ -1482,12 +1482,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1499,12 +1499,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'small'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Small'}</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -1516,12 +1516,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1533,12 +1533,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'large'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Large'}</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
@@ -1550,12 +1550,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'extra_large'}</t>
+          <t>extra_large</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'Extra Large'}</t>
+          <t>Extra Large</t>
         </is>
       </c>
     </row>
@@ -1567,12 +1567,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1584,12 +1584,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1618,12 +1618,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'utc'}</t>
+          <t>utc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'UTC'}</t>
+          <t>UTC</t>
         </is>
       </c>
     </row>
@@ -1635,12 +1635,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'local'}</t>
+          <t>local</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'Local'}</t>
+          <t>Local</t>
         </is>
       </c>
     </row>
